--- a/filesystem/Legal/Compliance/claims_review_signoff_log.xlsx
+++ b/filesystem/Legal/Compliance/claims_review_signoff_log.xlsx
@@ -159,7 +159,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -229,8 +229,28 @@
         <bgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -449,11 +469,114 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -567,6 +690,42 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -875,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -895,14 +1054,6 @@
           <t>Compliance Sign-Off Log — Claims Review Approvals</t>
         </is>
       </c>
-      <c r="B1" s="16" t="n"/>
-      <c r="C1" s="16" t="n"/>
-      <c r="D1" s="16" t="n"/>
-      <c r="E1" s="16" t="n"/>
-      <c r="F1" s="16" t="n"/>
-      <c r="G1" s="16" t="n"/>
-      <c r="H1" s="16" t="n"/>
-      <c r="I1" s="16" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="26" customHeight="1">
@@ -911,18 +1062,18 @@
           <t>Owner:</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Linh Vuong, Compliance &amp; Legal Counsel — Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-      <c r="E3" s="18" t="n"/>
-      <c r="F3" s="18" t="n"/>
-      <c r="G3" s="18" t="n"/>
-      <c r="H3" s="18" t="n"/>
-      <c r="I3" s="19" t="n"/>
+      <c r="C3" s="42" t="n"/>
+      <c r="D3" s="42" t="n"/>
+      <c r="E3" s="42" t="n"/>
+      <c r="F3" s="42" t="n"/>
+      <c r="G3" s="42" t="n"/>
+      <c r="H3" s="42" t="n"/>
+      <c r="I3" s="43" t="n"/>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
@@ -930,18 +1081,18 @@
           <t>Companion policy:</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Compliance Reserve &amp; Claims-Review Policy (09/15/2025)</t>
         </is>
       </c>
-      <c r="C4" s="18" t="n"/>
-      <c r="D4" s="18" t="n"/>
-      <c r="E4" s="18" t="n"/>
-      <c r="F4" s="18" t="n"/>
-      <c r="G4" s="18" t="n"/>
-      <c r="H4" s="18" t="n"/>
-      <c r="I4" s="19" t="n"/>
+      <c r="C4" s="42" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="42" t="n"/>
+      <c r="G4" s="42" t="n"/>
+      <c r="H4" s="42" t="n"/>
+      <c r="I4" s="43" t="n"/>
     </row>
     <row r="5" ht="85" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
@@ -949,18 +1100,18 @@
           <t>Purpose:</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Standing record of dispositions issued by Compliance for comparative and superiority claims made on behalf of regulated (diagnostics / instrumentation) clients under Section 3 of the companion policy. Where a regulated-client asset has been Creative-approved but contains a comparative or superiority claim, the asset is not shippable until the specific claim wording appears on this log with a cleared status. A cleared status attaches to the specific claim wording and creative version cleared, not to the client account as a whole. Absence of an entry for a given wording means the claim has not cleared claims review.</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
-      <c r="H5" s="18" t="n"/>
-      <c r="I5" s="19" t="n"/>
+      <c r="C5" s="42" t="n"/>
+      <c r="D5" s="42" t="n"/>
+      <c r="E5" s="42" t="n"/>
+      <c r="F5" s="42" t="n"/>
+      <c r="G5" s="42" t="n"/>
+      <c r="H5" s="42" t="n"/>
+      <c r="I5" s="43" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
@@ -968,34 +1119,34 @@
           <t>Last updated:</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>12/28/2025</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
-      <c r="H6" s="18" t="n"/>
-      <c r="I6" s="19" t="n"/>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="n"/>
+      <c r="D6" s="42" t="n"/>
+      <c r="E6" s="42" t="n"/>
+      <c r="F6" s="42" t="n"/>
+      <c r="G6" s="42" t="n"/>
+      <c r="H6" s="42" t="n"/>
+      <c r="I6" s="43" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1"/>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>Sign-Off Log</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
+      <c r="B8" s="44" t="n"/>
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
+      <c r="F8" s="44" t="n"/>
+      <c r="G8" s="44" t="n"/>
+      <c r="H8" s="44" t="n"/>
+      <c r="I8" s="44" t="n"/>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="21" t="inlineStr">
@@ -1097,7 +1248,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>Larkspur Diagnostic Instruments</t>
+          <t>Vantage Bioinstruments</t>
         </is>
       </c>
       <c r="C11" s="29" t="inlineStr">
@@ -1191,7 +1342,7 @@
       </c>
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>Penbrook Bio-Instruments</t>
+          <t>Norbury Bioimaging</t>
         </is>
       </c>
       <c r="C13" s="29" t="inlineStr">
@@ -1238,7 +1389,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Marston-Kline Diagnostics</t>
+          <t>Ingleton Diagnostics</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -1285,7 +1436,7 @@
       </c>
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Ridgemont Analytical Systems</t>
+          <t>Coppergate Diagnostics</t>
         </is>
       </c>
       <c r="C15" s="29" t="inlineStr">
@@ -1332,7 +1483,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Bellhaven Molecular Diagnostics</t>
+          <t>Redcliff Bioinstruments</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -1426,7 +1577,7 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Redgrove Assay Systems</t>
+          <t>Weybridge Scientific</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -1520,7 +1671,7 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Ashworth Analytical Instruments</t>
+          <t>Larchfield Bioanalytics</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -1567,7 +1718,7 @@
       </c>
       <c r="B21" s="29" t="inlineStr">
         <is>
-          <t>Kestrelburg Reagents &amp; Diagnostics</t>
+          <t>Coleridge Biotech Marketing</t>
         </is>
       </c>
       <c r="C21" s="29" t="inlineStr">
@@ -1614,7 +1765,7 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Ferncroft Instrumentation</t>
+          <t>Pennington Cell Therapy</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -1661,7 +1812,7 @@
       </c>
       <c r="B23" s="29" t="inlineStr">
         <is>
-          <t>Thistledown Molecular</t>
+          <t>Portishead Molecular</t>
         </is>
       </c>
       <c r="C23" s="29" t="inlineStr">
@@ -1745,46 +1896,301 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1"/>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="46" t="inlineStr">
+        <is>
+          <t>CSL-2025-0043</t>
+        </is>
+      </c>
+      <c r="B25" s="47" t="inlineStr">
+        <is>
+          <t>Hollowridge Molecular</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="inlineStr">
+        <is>
+          <t>Always-on paid search — clinical chemistry panel</t>
+        </is>
+      </c>
+      <c r="D25" s="47" t="inlineStr">
+        <is>
+          <t>Descriptive product-fact language for always-on paid search creative; no comparative or superiority phrasing asserted.</t>
+        </is>
+      </c>
+      <c r="E25" s="48" t="inlineStr">
+        <is>
+          <t>Ad_v1.0</t>
+        </is>
+      </c>
+      <c r="F25" s="48" t="inlineStr">
+        <is>
+          <t>Linh Vuong</t>
+        </is>
+      </c>
+      <c r="G25" s="49" t="n">
+        <v>45897</v>
+      </c>
+      <c r="H25" s="50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I25" s="47" t="inlineStr">
+        <is>
+          <t>Thornfield native. No comparative claims in current creative rotation. Scope confirmation only.</t>
+        </is>
+      </c>
+    </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="41" t="inlineStr">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>CSL-2025-0044</t>
+        </is>
+      </c>
+      <c r="B26" s="47" t="inlineStr">
+        <is>
+          <t>Ramsden Bioanalytics</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>Q4 2025 congress sponsorship</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="inlineStr">
+        <is>
+          <t>Descriptive congress-sponsorship creative; no comparative or superiority phrasing asserted.</t>
+        </is>
+      </c>
+      <c r="E26" s="48" t="inlineStr">
+        <is>
+          <t>Deck_v1.1</t>
+        </is>
+      </c>
+      <c r="F26" s="48" t="inlineStr">
+        <is>
+          <t>Linh Vuong</t>
+        </is>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>10/22/2025</t>
+        </is>
+      </c>
+      <c r="H26" s="50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I26" s="47" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell. Historical Bramwell reserve-classification memo (superseded 09/15/2025) removed from client-facing decks. No comparative claim in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>CSL-2025-0045</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>Trentham Diagnostics</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>Q1 2026 payer-audience campaign</t>
+        </is>
+      </c>
+      <c r="D27" s="47" t="inlineStr">
+        <is>
+          <t>"Clinically validated across [n] sites" — comparative claim with multi-site study citation.</t>
+        </is>
+      </c>
+      <c r="E27" s="48" t="inlineStr">
+        <is>
+          <t>Brief_v1.2</t>
+        </is>
+      </c>
+      <c r="F27" s="48" t="inlineStr">
+        <is>
+          <t>Linh Vuong</t>
+        </is>
+      </c>
+      <c r="G27" s="49" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="H27" s="50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I27" s="47" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell. Cleared with study citation on file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="51" t="inlineStr">
+        <is>
+          <t>CSL-2025-0046</t>
+        </is>
+      </c>
+      <c r="B28" s="52" t="inlineStr">
+        <is>
+          <t>Marchmont Analytical Systems</t>
+        </is>
+      </c>
+      <c r="C28" s="52" t="inlineStr">
+        <is>
+          <t>Q1 2026 distributor co-marketing</t>
+        </is>
+      </c>
+      <c r="D28" s="52" t="inlineStr">
+        <is>
+          <t>Co-branded descriptive creative; distributor-side claims outside Thornfield Section 3 scope.</t>
+        </is>
+      </c>
+      <c r="E28" s="53" t="inlineStr">
+        <is>
+          <t>Brief_v1.0</t>
+        </is>
+      </c>
+      <c r="F28" s="53" t="inlineStr">
+        <is>
+          <t>Linh Vuong</t>
+        </is>
+      </c>
+      <c r="G28" s="54" t="n">
+        <v>46010</v>
+      </c>
+      <c r="H28" s="55" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I28" s="52" t="inlineStr">
+        <is>
+          <t>Thornfield native. Co-branded creative reviewed under Section 3; distributor-side claims out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="46" t="inlineStr">
+        <is>
+          <t>CSL-2025-0047</t>
+        </is>
+      </c>
+      <c r="B29" s="47" t="inlineStr">
+        <is>
+          <t>Ellstone Diagnostics</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>Q1 2026 veterinary-clinic direct</t>
+        </is>
+      </c>
+      <c r="D29" s="47" t="inlineStr">
+        <is>
+          <t>Comparative accuracy claim for veterinary diagnostics segment, with substantiation on file.</t>
+        </is>
+      </c>
+      <c r="E29" s="48" t="inlineStr">
+        <is>
+          <t>Brief_v1.1</t>
+        </is>
+      </c>
+      <c r="F29" s="48" t="inlineStr">
+        <is>
+          <t>Linh Vuong</t>
+        </is>
+      </c>
+      <c r="G29" s="49" t="n">
+        <v>45990</v>
+      </c>
+      <c r="H29" s="50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I29" s="47" t="inlineStr">
+        <is>
+          <t>Thornfield native. Veterinary segment carries same Section 3 obligations under this roster; comparative accuracy claim cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>CSL-2025-0048</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="inlineStr">
+        <is>
+          <t>Prescott Bio-Analytical</t>
+        </is>
+      </c>
+      <c r="C30" s="52" t="inlineStr">
+        <is>
+          <t>Q4 2025 whitepaper series</t>
+        </is>
+      </c>
+      <c r="D30" s="52" t="inlineStr">
+        <is>
+          <t>Two claims reviewed: one cleared descriptive benchmark claim, one comparative claim held pending updated benchmark data.</t>
+        </is>
+      </c>
+      <c r="E30" s="53" t="inlineStr">
+        <is>
+          <t>Whitepaper_v1.3</t>
+        </is>
+      </c>
+      <c r="F30" s="53" t="inlineStr">
+        <is>
+          <t>Linh Vuong</t>
+        </is>
+      </c>
+      <c r="G30" s="54" t="n">
+        <v>45996</v>
+      </c>
+      <c r="H30" s="55" t="inlineStr">
+        <is>
+          <t>Approved (in part)</t>
+        </is>
+      </c>
+      <c r="I30" s="52" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell. Two claims cleared, one held pending updated benchmark data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t>Prepared and maintained by: Linh Vuong, Compliance &amp; Legal Counsel — Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="B26" s="41" t="n"/>
-      <c r="C26" s="41" t="n"/>
-      <c r="D26" s="41" t="n"/>
-      <c r="E26" s="41" t="n"/>
-      <c r="F26" s="41" t="n"/>
-      <c r="G26" s="41" t="n"/>
-      <c r="H26" s="41" t="n"/>
-      <c r="I26" s="41" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="41" t="inlineStr">
-        <is>
-          <t>Last updated: 12/28/2025</t>
-        </is>
-      </c>
-      <c r="B27" s="41" t="n"/>
-      <c r="C27" s="41" t="n"/>
-      <c r="D27" s="41" t="n"/>
-      <c r="E27" s="41" t="n"/>
-      <c r="F27" s="41" t="n"/>
-      <c r="G27" s="41" t="n"/>
-      <c r="H27" s="41" t="n"/>
-      <c r="I27" s="41" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>Last updated: 01/10/2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="6">
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A26:I26"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/filesystem/Legal/Compliance/claims_review_signoff_log.xlsx
+++ b/filesystem/Legal/Compliance/claims_review_signoff_log.xlsx
@@ -1896,7 +1896,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="42" customHeight="1">
       <c r="A25" s="46" t="inlineStr">
         <is>
           <t>CSL-2025-0043</t>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="42" customHeight="1">
       <c r="A26" s="46" t="inlineStr">
         <is>
           <t>CSL-2025-0044</t>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="46" t="inlineStr">
         <is>
           <t>CSL-2025-0045</t>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="I28" s="52" t="inlineStr">
         <is>
-          <t>Thornfield native. Co-branded creative reviewed under Section 3; distributor-side claims out of scope.</t>
+          <t>Inherited — Bramwell. Co-branded creative reviewed under Section 3; distributor-side claims out of scope.</t>
         </is>
       </c>
     </row>

--- a/filesystem/Legal/Compliance/claims_review_signoff_log.xlsx
+++ b/filesystem/Legal/Compliance/claims_review_signoff_log.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -156,6 +156,12 @@
       <name val="Segoe UI"/>
       <i val="1"/>
       <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF475569"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -576,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -726,6 +732,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1822,7 +1831,7 @@
       </c>
       <c r="D23" s="29" t="inlineStr">
         <is>
-          <t>"Expanded panel coverage across [target list]" — descriptive; separate turnaround claim withdrawn by Creative before review.</t>
+          <t>"Expanded panel coverage across 48 oncology-relevant gene targets" — descriptive; separate turnaround claim withdrawn by Creative before review.</t>
         </is>
       </c>
       <c r="E23" s="30" t="inlineStr">
@@ -2006,7 +2015,7 @@
       </c>
       <c r="D27" s="47" t="inlineStr">
         <is>
-          <t>"Clinically validated across [n] sites" — comparative claim with multi-site study citation.</t>
+          <t>"Clinically validated across 14 clinical sites" — comparative claim with multi-site study citation.</t>
         </is>
       </c>
       <c r="E27" s="48" t="inlineStr">
@@ -2170,15 +2179,16 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
-      <c r="A32" s="41" t="inlineStr">
+      <c r="A32" s="56" t="inlineStr">
         <is>
           <t>Prepared and maintained by: Linh Vuong, Compliance &amp; Legal Counsel — Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="41" t="inlineStr">
+      <c r="A33" s="56" t="inlineStr">
         <is>
           <t>Last updated: 01/10/2026</t>
         </is>
